--- a/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="92">
   <si>
     <t>MAKSY</t>
   </si>
@@ -656,75 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45835</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45471</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -764,8 +771,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,8 +818,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -846,8 +865,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +888,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,8 +931,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,8 +978,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,8 +1025,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1027,8 +1072,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,8 +1092,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1082,8 +1135,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1123,8 +1182,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,8 +1205,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1181,8 +1248,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1222,8 +1295,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1263,8 +1342,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1304,8 +1389,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1345,8 +1436,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,8 +1483,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1427,8 +1530,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1468,8 +1577,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1624,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1671,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1718,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,8 +1765,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1673,8 +1812,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1714,8 +1859,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,8 +1906,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1796,54 +1953,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45835</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45471</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +2028,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,377 +2047,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1325200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1344800</v>
+      </c>
+      <c r="F41" s="3">
         <v>1030900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1054200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1119100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1088400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>829100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>781900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1291300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1302300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1011300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1053100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1321100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1286700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F42" s="3">
         <v>107100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>109600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>367900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>357800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>216700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>204400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>9600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>9700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>11000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>11400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>9200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>531100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>538900</v>
+      </c>
+      <c r="F43" s="3">
         <v>985300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1007600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>351500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>341800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>521100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>491500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>285300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>287700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>389900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>406000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>235200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>229000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1304200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1323500</v>
+      </c>
+      <c r="F44" s="3">
         <v>1598900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1635100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1092500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1062500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1313100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1238400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>981200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>989600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1219900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1270400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>945700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>921000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>27900</v>
+      </c>
+      <c r="F45" s="3">
         <v>9800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>10000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>16200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>15700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>10100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>14500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>14600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>30900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>32200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>34900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3444000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3494800</v>
+      </c>
+      <c r="F46" s="3">
         <v>3732000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3816400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3111700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3026400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2890100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2725600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2719600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2742800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2663000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2773100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2666000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2596500</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>71600</v>
+      </c>
+      <c r="F47" s="3">
         <v>86600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>88600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>535700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>521000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>898900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>847800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>880000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>887600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>895500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>932500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>959800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>934800</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8517700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8643200</v>
+      </c>
+      <c r="F48" s="3">
         <v>8222900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8408900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7001600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6809600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6984000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6586600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6555000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6610900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>6247300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6505700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6437700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6269900</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1002200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1016900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1035600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1059000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>242600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>235900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>228100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>215100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>226700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>228600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>219000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>228100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>201800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>196500</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2513,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,49 +2560,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>308300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>312900</v>
+      </c>
+      <c r="F52" s="3">
         <v>17800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>18200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>297400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>289200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>92500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>87200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>374600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>377800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>246600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>256800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>863500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>841000</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,49 +2654,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13442100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13640300</v>
+      </c>
+      <c r="F54" s="3">
         <v>13500400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13805900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11419700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11106600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11632700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10970800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10965400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11059000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10706200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11149100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>11255200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10961900</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2724,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,254 +2743,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1397900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1418500</v>
+      </c>
+      <c r="F57" s="3">
         <v>3914100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4002700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1030800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1002600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2857900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2695300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>962800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>971000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2613800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2721900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>991800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>966000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>402800</v>
+      </c>
+      <c r="F58" s="3">
         <v>541800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>554000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>460600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>448000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>443100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>417900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>316200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>318900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>409300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>426200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>549300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>535000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1161500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1178600</v>
+      </c>
+      <c r="F59" s="3">
         <v>152700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>156200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1150500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1118900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>154400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>145600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>866000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>873400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>141800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>147700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>925300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>901100</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3983000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4041700</v>
+      </c>
+      <c r="F60" s="3">
         <v>4608600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4712900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3595600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3497000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3521300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3321000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3177900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3205000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3320000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3457300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3348200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3260900</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4158400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4219700</v>
+      </c>
+      <c r="F61" s="3">
         <v>4010400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4101100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3351200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3259300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3421400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3226700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3640900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3672000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3607900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3757100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3939000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3836400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>267100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>271100</v>
+      </c>
+      <c r="F62" s="3">
         <v>293800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>300500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>212200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>206400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>342400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>322900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>290000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>292500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>251400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>261800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>308200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>300100</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +3068,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +3115,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,49 +3162,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9159000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9294000</v>
+      </c>
+      <c r="F66" s="3">
         <v>9516300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9731600</v>
       </c>
-      <c r="F66" s="3">
-        <v>7599000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>7390600</v>
-      </c>
       <c r="H66" s="3">
+        <v>7753700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>7541100</v>
+      </c>
+      <c r="J66" s="3">
         <v>7571100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7140300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7391100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7454100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>7231300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7530500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7938700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7731800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3232,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3275,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3322,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3369,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,49 +3416,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7950900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8068100</v>
+      </c>
+      <c r="F72" s="3">
         <v>7719200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>7893800</v>
       </c>
-      <c r="F72" s="3">
-        <v>7622900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>7413900</v>
-      </c>
       <c r="H72" s="3">
+        <v>7468300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>7263500</v>
+      </c>
+      <c r="J72" s="3">
         <v>8069400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7610300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7312100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7374500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>7108200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>7402200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>7057800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>6873900</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3510,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3557,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3604,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4061400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4121300</v>
+      </c>
+      <c r="F76" s="3">
         <v>3755300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3840300</v>
       </c>
-      <c r="F76" s="3">
-        <v>3806100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>3701700</v>
-      </c>
       <c r="H76" s="3">
+        <v>3651400</v>
+      </c>
+      <c r="I76" s="3">
+        <v>3551300</v>
+      </c>
+      <c r="J76" s="3">
         <v>4067800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3836400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3575700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3606300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3470800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3614400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3311100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3224800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,54 +3698,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45835</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45471</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3408,8 +3797,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,49 +3820,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>95600</v>
+      </c>
+      <c r="F83" s="3">
         <v>167600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>158000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>119500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>120600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>153800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>160100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>149300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>145400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>135700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>146500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>134300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>138800</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3910,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3957,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +4004,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +4051,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +4098,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>671300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>681200</v>
+      </c>
+      <c r="F89" s="3">
         <v>111100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>113600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>593700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>577400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>265200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>250100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>517500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>521900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>294200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>306400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>451500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>439700</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,49 +4168,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-271800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-275800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-111200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-113700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-157500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-153200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-110600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-104300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-125100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-126200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-98500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-102600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-112700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-109800</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4258,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,49 +4305,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-289100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-293400</v>
+      </c>
+      <c r="F94" s="3">
         <v>66000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>67500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-229900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-223600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-228400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-215400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-139700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-140900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-130600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-136000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-154000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-149900</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,49 +4375,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F96" s="3">
         <v>35100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>35900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>13100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>12800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>26900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>25400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>12400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>12500</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4465,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4512,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,127 +4559,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-229600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-233000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-240400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-245800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-204700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-199100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-306500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-289000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-254600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-256700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-309200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-322000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-112100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-109200</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-5500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-5700</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>151800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>154100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-64200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-65700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>159100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>154700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-270500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-255100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>122300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>123400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-145900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-152000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>182600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>177800</v>
       </c>
     </row>
